--- a/config/generated/templates/BattleResultProjectionField.xlsx
+++ b/config/generated/templates/BattleResultProjectionField.xlsx
@@ -31,16 +31,16 @@
     <t>@key</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>b3a645e6a59b7aa1</t>
+    <t>29d7af0ac52ce46d</t>
   </si>
   <si>
     <t>#name</t>
@@ -70,7 +70,7 @@
     <t>union&lt;BattleResultProjectionFieldNode&gt;</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
